--- a/assets/templates/excel/pivot-demo.xlsx
+++ b/assets/templates/excel/pivot-demo.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据透视" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,7 +27,13 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="002B579A"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,8 +45,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="002B579A"/>
+        <bgColor rgb="002B579A"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -426,71 +435,103 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>类别</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>数值1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>数值2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>数值3</t>
+          <t>DATA ANALYSIS / 数据分析</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>示例数据</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>示例数据</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>示例数据</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>示例数据</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>示例数据</t>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>{{category}}</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>{{item}}</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>{{q1_value}}</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{{q2_value}}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>{{q3_value}}</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>{{q4_value}}</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>{{total}}</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>